--- a/stock_recommendations_20260501.xlsx
+++ b/stock_recommendations_20260501.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票建議" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FinRL改善" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -809,7 +808,7 @@
         <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -874,228 +873,6 @@
           <t>2026-05-01</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>檔案</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>狀態</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>優先度</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1. 增強版 Reward Function</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>environments/reward_function_v2.py</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>✅ 已完成</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>🔴 高</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Sortino Ratio 獎勵</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Calmar Ratio 獎勵</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 波動度懲罰</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Inactivity 懲罰</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2. 增強版 Risk Manager</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>risk_manager_v2.py</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>✅ 已完成</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>🔴 高</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Early Stopping</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 動態 Kelly 倉位</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 單日虧損檢查</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 完整風控信號</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3. 增強版 Walk-Forward</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>walk_forward_v2.py</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>✅ 已完成</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>🟡 中</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 統計顯著性檢驗</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 風險等級分類</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - JSON 報告輸出</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Monte Carlo 框架</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
